--- a/Back-End/Document/List_API_v2_67APIs.xlsx
+++ b/Back-End/Document/List_API_v2_67APIs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project E-commerce Web\Back-end\Tài liệu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Final-Project_Tech\Back-End\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FACCAE-E583-4DDD-835C-AA8377598AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2016213-8F18-4FA8-BC84-A23F93F5F048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -118,9 +118,6 @@
     <t>GET</t>
   </si>
   <si>
-    <t>/api/v1/me</t>
-  </si>
-  <si>
     <t>Lấy thông tin cá nhân user đang đăng nhập kèm danh sách roles.</t>
   </si>
   <si>
@@ -136,9 +133,6 @@
     <t>Change Password</t>
   </si>
   <si>
-    <t>/api/v1/me/password</t>
-  </si>
-  <si>
     <t>Đổi mật khẩu khi đã đăng nhập. Yêu cầu nhập mật khẩu cũ để xác nhận.</t>
   </si>
   <si>
@@ -713,6 +707,12 @@
   </si>
   <si>
     <t xml:space="preserve">68 APIs  </t>
+  </si>
+  <si>
+    <t>/api/v1/users/me</t>
+  </si>
+  <si>
+    <t>/api/v1/users/me/password</t>
   </si>
 </sst>
 </file>
@@ -1673,10 +1673,10 @@
         <v>31</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>32</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>33</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>12</v>
@@ -1690,16 +1690,16 @@
         <v>29</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="E9" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>36</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>12</v>
@@ -1713,16 +1713,16 @@
         <v>29</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>37</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>39</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>12</v>
@@ -1733,22 +1733,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>31</v>
       </c>
       <c r="E11" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="17" t="s">
         <v>42</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1756,22 +1756,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D12" s="18" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="17" t="s">
         <v>42</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1779,22 +1779,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C13" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>49</v>
-      </c>
       <c r="G13" s="17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1802,22 +1802,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C14" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>52</v>
-      </c>
       <c r="G14" s="17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1825,22 +1825,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C15" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>55</v>
-      </c>
       <c r="G15" s="17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1848,19 +1848,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D16" s="24" t="s">
         <v>31</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G16" s="25" t="s">
         <v>16</v>
@@ -1871,19 +1871,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D17" s="29" t="s">
         <v>31</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G17" s="30" t="s">
         <v>16</v>
@@ -1894,19 +1894,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D18" s="29" t="s">
         <v>31</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G18" s="30" t="s">
         <v>16</v>
@@ -1917,19 +1917,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D19" s="34" t="s">
         <v>31</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F19" s="33" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G19" s="35" t="s">
         <v>16</v>
@@ -1940,19 +1940,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D20" s="34" t="s">
         <v>31</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F20" s="33" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G20" s="35" t="s">
         <v>16</v>
@@ -1963,19 +1963,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D21" s="34" t="s">
         <v>31</v>
       </c>
       <c r="E21" s="32" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F21" s="33" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G21" s="35" t="s">
         <v>16</v>
@@ -1986,22 +1986,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D22" s="39" t="s">
         <v>9</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G22" s="40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2009,22 +2009,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D23" s="41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E23" s="37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G23" s="40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2032,22 +2032,22 @@
         <v>23</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D24" s="42" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G24" s="40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2055,22 +2055,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D25" s="43" t="s">
         <v>31</v>
       </c>
       <c r="E25" s="37" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F25" s="38" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G25" s="40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2078,22 +2078,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D26" s="43" t="s">
         <v>31</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G26" s="40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2101,19 +2101,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D27" s="46" t="s">
         <v>31</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F27" s="45" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G27" s="47" t="s">
         <v>16</v>
@@ -2124,22 +2124,22 @@
         <v>27</v>
       </c>
       <c r="B28" s="44" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D28" s="46" t="s">
         <v>31</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F28" s="45" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G28" s="47" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2147,22 +2147,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="44" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C29" s="45" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D29" s="48" t="s">
         <v>9</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F29" s="45" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G29" s="47" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2170,22 +2170,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="44" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D30" s="49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F30" s="45" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G30" s="47" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2193,22 +2193,22 @@
         <v>30</v>
       </c>
       <c r="B31" s="50" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C31" s="51" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D31" s="52" t="s">
         <v>31</v>
       </c>
       <c r="E31" s="50" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G31" s="53" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2216,22 +2216,22 @@
         <v>31</v>
       </c>
       <c r="B32" s="50" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D32" s="54" t="s">
         <v>9</v>
       </c>
       <c r="E32" s="50" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F32" s="51" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G32" s="53" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2239,22 +2239,22 @@
         <v>32</v>
       </c>
       <c r="B33" s="50" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C33" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="F33" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="D33" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="E33" s="50" t="s">
-        <v>110</v>
-      </c>
-      <c r="F33" s="51" t="s">
-        <v>111</v>
-      </c>
       <c r="G33" s="53" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2262,22 +2262,22 @@
         <v>33</v>
       </c>
       <c r="B34" s="50" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C34" s="51" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D34" s="56" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E34" s="50" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F34" s="51" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G34" s="53" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2285,22 +2285,22 @@
         <v>34</v>
       </c>
       <c r="B35" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="D35" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="E35" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C35" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="D35" s="56" t="s">
-        <v>51</v>
-      </c>
-      <c r="E35" s="50" t="s">
-        <v>104</v>
-      </c>
       <c r="F35" s="51" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G35" s="53" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2308,22 +2308,22 @@
         <v>35</v>
       </c>
       <c r="B36" s="57" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C36" s="58" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D36" s="59" t="s">
         <v>9</v>
       </c>
       <c r="E36" s="57" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F36" s="58" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G36" s="60" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2331,22 +2331,22 @@
         <v>36</v>
       </c>
       <c r="B37" s="57" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C37" s="58" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D37" s="61" t="s">
         <v>31</v>
       </c>
       <c r="E37" s="57" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F37" s="58" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G37" s="60" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2354,22 +2354,22 @@
         <v>37</v>
       </c>
       <c r="B38" s="57" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C38" s="58" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D38" s="61" t="s">
         <v>31</v>
       </c>
       <c r="E38" s="57" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F38" s="58" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G38" s="60" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2377,22 +2377,22 @@
         <v>38</v>
       </c>
       <c r="B39" s="57" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C39" s="58" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D39" s="59" t="s">
         <v>9</v>
       </c>
       <c r="E39" s="57" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F39" s="58" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G39" s="60" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2400,22 +2400,22 @@
         <v>39</v>
       </c>
       <c r="B40" s="62" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C40" s="63" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D40" s="64" t="s">
         <v>31</v>
       </c>
       <c r="E40" s="62" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F40" s="63" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G40" s="65" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2423,22 +2423,22 @@
         <v>40</v>
       </c>
       <c r="B41" s="62" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C41" s="63" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D41" s="64" t="s">
         <v>31</v>
       </c>
       <c r="E41" s="62" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F41" s="63" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G41" s="65" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2446,22 +2446,22 @@
         <v>41</v>
       </c>
       <c r="B42" s="62" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C42" s="63" t="s">
+        <v>132</v>
+      </c>
+      <c r="D42" s="66" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42" s="62" t="s">
+        <v>133</v>
+      </c>
+      <c r="F42" s="63" t="s">
         <v>134</v>
       </c>
-      <c r="D42" s="66" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" s="62" t="s">
-        <v>135</v>
-      </c>
-      <c r="F42" s="63" t="s">
-        <v>136</v>
-      </c>
       <c r="G42" s="65" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2469,22 +2469,22 @@
         <v>42</v>
       </c>
       <c r="B43" s="62" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C43" s="63" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D43" s="64" t="s">
         <v>31</v>
       </c>
       <c r="E43" s="62" t="s">
+        <v>136</v>
+      </c>
+      <c r="F43" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="G43" s="65" t="s">
         <v>138</v>
-      </c>
-      <c r="F43" s="63" t="s">
-        <v>139</v>
-      </c>
-      <c r="G43" s="65" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2492,22 +2492,22 @@
         <v>43</v>
       </c>
       <c r="B44" s="67" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C44" s="68" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D44" s="69" t="s">
         <v>9</v>
       </c>
       <c r="E44" s="67" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F44" s="68" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G44" s="70" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2515,22 +2515,22 @@
         <v>44</v>
       </c>
       <c r="B45" s="67" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C45" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="D45" s="71" t="s">
+        <v>34</v>
+      </c>
+      <c r="E45" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="F45" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="D45" s="71" t="s">
-        <v>35</v>
-      </c>
-      <c r="E45" s="67" t="s">
+      <c r="G45" s="70" t="s">
         <v>146</v>
-      </c>
-      <c r="F45" s="68" t="s">
-        <v>147</v>
-      </c>
-      <c r="G45" s="70" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2538,22 +2538,22 @@
         <v>45</v>
       </c>
       <c r="B46" s="72" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C46" s="73" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D46" s="74" t="s">
         <v>31</v>
       </c>
       <c r="E46" s="72" t="s">
+        <v>149</v>
+      </c>
+      <c r="F46" s="73" t="s">
+        <v>150</v>
+      </c>
+      <c r="G46" s="75" t="s">
         <v>151</v>
-      </c>
-      <c r="F46" s="73" t="s">
-        <v>152</v>
-      </c>
-      <c r="G46" s="75" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2561,22 +2561,22 @@
         <v>46</v>
       </c>
       <c r="B47" s="72" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C47" s="73" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D47" s="76" t="s">
         <v>9</v>
       </c>
       <c r="E47" s="72" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F47" s="73" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G47" s="75" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2584,22 +2584,22 @@
         <v>47</v>
       </c>
       <c r="B48" s="72" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C48" s="73" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D48" s="74" t="s">
         <v>31</v>
       </c>
       <c r="E48" s="72" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F48" s="73" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G48" s="75" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2607,22 +2607,22 @@
         <v>48</v>
       </c>
       <c r="B49" s="72" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C49" s="73" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D49" s="76" t="s">
         <v>9</v>
       </c>
       <c r="E49" s="72" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F49" s="73" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G49" s="75" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2630,22 +2630,22 @@
         <v>49</v>
       </c>
       <c r="B50" s="72" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C50" s="73" t="s">
+        <v>159</v>
+      </c>
+      <c r="D50" s="77" t="s">
+        <v>34</v>
+      </c>
+      <c r="E50" s="72" t="s">
+        <v>160</v>
+      </c>
+      <c r="F50" s="73" t="s">
         <v>161</v>
       </c>
-      <c r="D50" s="77" t="s">
-        <v>35</v>
-      </c>
-      <c r="E50" s="72" t="s">
-        <v>162</v>
-      </c>
-      <c r="F50" s="73" t="s">
-        <v>163</v>
-      </c>
       <c r="G50" s="75" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2653,22 +2653,22 @@
         <v>50</v>
       </c>
       <c r="B51" s="78" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C51" s="79" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D51" s="80" t="s">
         <v>31</v>
       </c>
       <c r="E51" s="78" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F51" s="79" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G51" s="81" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2676,22 +2676,22 @@
         <v>51</v>
       </c>
       <c r="B52" s="78" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C52" s="79" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D52" s="82" t="s">
         <v>9</v>
       </c>
       <c r="E52" s="78" t="s">
+        <v>167</v>
+      </c>
+      <c r="F52" s="79" t="s">
+        <v>168</v>
+      </c>
+      <c r="G52" s="81" t="s">
         <v>169</v>
-      </c>
-      <c r="F52" s="79" t="s">
-        <v>170</v>
-      </c>
-      <c r="G52" s="81" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2699,22 +2699,22 @@
         <v>52</v>
       </c>
       <c r="B53" s="78" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C53" s="79" t="s">
+        <v>170</v>
+      </c>
+      <c r="D53" s="83" t="s">
+        <v>34</v>
+      </c>
+      <c r="E53" s="78" t="s">
+        <v>171</v>
+      </c>
+      <c r="F53" s="79" t="s">
         <v>172</v>
       </c>
-      <c r="D53" s="83" t="s">
-        <v>35</v>
-      </c>
-      <c r="E53" s="78" t="s">
-        <v>173</v>
-      </c>
-      <c r="F53" s="79" t="s">
-        <v>174</v>
-      </c>
       <c r="G53" s="81" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2722,22 +2722,22 @@
         <v>53</v>
       </c>
       <c r="B54" s="84" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C54" s="85" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D54" s="86" t="s">
         <v>31</v>
       </c>
       <c r="E54" s="84" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F54" s="85" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G54" s="87" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2745,22 +2745,22 @@
         <v>54</v>
       </c>
       <c r="B55" s="84" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C55" s="85" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D55" s="86" t="s">
         <v>31</v>
       </c>
       <c r="E55" s="84" t="s">
+        <v>178</v>
+      </c>
+      <c r="F55" s="85" t="s">
+        <v>179</v>
+      </c>
+      <c r="G55" s="87" t="s">
         <v>180</v>
-      </c>
-      <c r="F55" s="85" t="s">
-        <v>181</v>
-      </c>
-      <c r="G55" s="87" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2768,22 +2768,22 @@
         <v>55</v>
       </c>
       <c r="B56" s="84" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C56" s="85" t="s">
+        <v>181</v>
+      </c>
+      <c r="D56" s="88" t="s">
+        <v>34</v>
+      </c>
+      <c r="E56" s="84" t="s">
+        <v>182</v>
+      </c>
+      <c r="F56" s="85" t="s">
         <v>183</v>
       </c>
-      <c r="D56" s="88" t="s">
-        <v>35</v>
-      </c>
-      <c r="E56" s="84" t="s">
-        <v>184</v>
-      </c>
-      <c r="F56" s="85" t="s">
-        <v>185</v>
-      </c>
       <c r="G56" s="87" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2791,22 +2791,22 @@
         <v>56</v>
       </c>
       <c r="B57" s="84" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C57" s="85" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D57" s="89" t="s">
         <v>9</v>
       </c>
       <c r="E57" s="84" t="s">
+        <v>184</v>
+      </c>
+      <c r="F57" s="85" t="s">
+        <v>185</v>
+      </c>
+      <c r="G57" s="87" t="s">
         <v>186</v>
-      </c>
-      <c r="F57" s="85" t="s">
-        <v>187</v>
-      </c>
-      <c r="G57" s="87" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2814,22 +2814,22 @@
         <v>57</v>
       </c>
       <c r="B58" s="90" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C58" s="91" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D58" s="92" t="s">
         <v>31</v>
       </c>
       <c r="E58" s="90" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F58" s="91" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G58" s="93" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2837,22 +2837,22 @@
         <v>58</v>
       </c>
       <c r="B59" s="90" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C59" s="91" t="s">
+        <v>191</v>
+      </c>
+      <c r="D59" s="94" t="s">
+        <v>34</v>
+      </c>
+      <c r="E59" s="90" t="s">
+        <v>192</v>
+      </c>
+      <c r="F59" s="91" t="s">
         <v>193</v>
       </c>
-      <c r="D59" s="94" t="s">
-        <v>35</v>
-      </c>
-      <c r="E59" s="90" t="s">
-        <v>194</v>
-      </c>
-      <c r="F59" s="91" t="s">
-        <v>195</v>
-      </c>
       <c r="G59" s="93" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2860,22 +2860,22 @@
         <v>59</v>
       </c>
       <c r="B60" s="90" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C60" s="91" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D60" s="95" t="s">
         <v>9</v>
       </c>
       <c r="E60" s="90" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F60" s="91" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G60" s="93" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2883,22 +2883,22 @@
         <v>60</v>
       </c>
       <c r="B61" s="90" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C61" s="91" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D61" s="92" t="s">
         <v>31</v>
       </c>
       <c r="E61" s="90" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F61" s="91" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G61" s="93" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2906,22 +2906,22 @@
         <v>61</v>
       </c>
       <c r="B62" s="90" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C62" s="91" t="s">
+        <v>200</v>
+      </c>
+      <c r="D62" s="94" t="s">
+        <v>34</v>
+      </c>
+      <c r="E62" s="90" t="s">
+        <v>201</v>
+      </c>
+      <c r="F62" s="91" t="s">
         <v>202</v>
       </c>
-      <c r="D62" s="94" t="s">
-        <v>35</v>
-      </c>
-      <c r="E62" s="90" t="s">
-        <v>203</v>
-      </c>
-      <c r="F62" s="91" t="s">
-        <v>204</v>
-      </c>
       <c r="G62" s="93" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2929,22 +2929,22 @@
         <v>62</v>
       </c>
       <c r="B63" s="90" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C63" s="91" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D63" s="92" t="s">
         <v>31</v>
       </c>
       <c r="E63" s="90" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F63" s="91" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G63" s="93" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2952,22 +2952,22 @@
         <v>63</v>
       </c>
       <c r="B64" s="90" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C64" s="91" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D64" s="92" t="s">
         <v>31</v>
       </c>
       <c r="E64" s="90" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F64" s="91" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G64" s="93" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2975,22 +2975,22 @@
         <v>64</v>
       </c>
       <c r="B65" s="90" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C65" s="91" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D65" s="95" t="s">
         <v>9</v>
       </c>
       <c r="E65" s="90" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F65" s="91" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G65" s="93" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2998,22 +2998,22 @@
         <v>65</v>
       </c>
       <c r="B66" s="90" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C66" s="91" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D66" s="95" t="s">
         <v>9</v>
       </c>
       <c r="E66" s="90" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F66" s="91" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G66" s="93" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3021,22 +3021,22 @@
         <v>66</v>
       </c>
       <c r="B67" s="90" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C67" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D67" s="94" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E67" s="90" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F67" s="91" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G67" s="93" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3044,22 +3044,22 @@
         <v>67</v>
       </c>
       <c r="B68" s="90" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C68" s="91" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D68" s="96" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E68" s="90" t="s">
+        <v>214</v>
+      </c>
+      <c r="F68" s="91" t="s">
         <v>216</v>
       </c>
-      <c r="F68" s="91" t="s">
-        <v>218</v>
-      </c>
       <c r="G68" s="93" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3067,33 +3067,33 @@
         <v>68</v>
       </c>
       <c r="B69" s="90" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C69" s="91" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D69" s="96" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E69" s="90" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F69" s="91" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G69" s="93" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>

--- a/Back-End/Document/List_API_v2_67APIs.xlsx
+++ b/Back-End/Document/List_API_v2_67APIs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Final-Project_Tech\Back-End\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2016213-8F18-4FA8-BC84-A23F93F5F048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F67CDA52-E83D-406D-A073-1CE4B96459EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -706,13 +706,13 @@
     <t xml:space="preserve">Revoke Role khỏi User </t>
   </si>
   <si>
-    <t xml:space="preserve">68 APIs  </t>
-  </si>
-  <si>
     <t>/api/v1/users/me</t>
   </si>
   <si>
     <t>/api/v1/users/me/password</t>
+  </si>
+  <si>
+    <t>68 APIs  Đã bổ sung</t>
   </si>
 </sst>
 </file>
@@ -1673,7 +1673,7 @@
         <v>31</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>32</v>
@@ -1696,7 +1696,7 @@
         <v>34</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>35</v>
@@ -1719,7 +1719,7 @@
         <v>34</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>37</v>
@@ -3093,7 +3093,7 @@
         <v>220</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
